--- a/data/trans_orig/barthel_r-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/barthel_r-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2007</t>
+          <t>Población según el grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>304481</t>
+          <t>304610</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>329801</t>
+          <t>329192</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>442835</t>
+          <t>439678</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>480921</t>
+          <t>481240</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,82%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>754035</t>
+          <t>753379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>802396</t>
+          <t>799743</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12682</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29457</t>
+          <t>30397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31365</t>
+          <t>32751</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56868</t>
+          <t>59051</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49037</t>
+          <t>49040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79894</t>
+          <t>80669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16339</t>
+          <t>17347</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34556</t>
+          <t>35500</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40800</t>
+          <t>40386</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68420</t>
+          <t>69180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62061</t>
+          <t>64089</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96538</t>
+          <t>96635</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>5382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16156</t>
+          <t>16505</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37205</t>
+          <t>37999</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25089</t>
+          <t>25629</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49687</t>
+          <t>48641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4227</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>11466</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74727</t>
+          <t>74774</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84724</t>
+          <t>84743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46908</t>
+          <t>47687</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58905</t>
+          <t>58777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,4%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126306</t>
+          <t>126670</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141651</t>
+          <t>141853</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1683</t>
+          <t>1720</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8321</t>
+          <t>9136</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13887</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9111</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11525</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4578</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6048</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,7 +1844,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1867,97 +1867,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1875</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5762</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>9,26%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>5663</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6655</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>9,1%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6801</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>30679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40242</t>
+          <t>40229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25690</t>
+          <t>25607</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51827</t>
+          <t>52519</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64413</t>
+          <t>64667</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>4824</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>866</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,48%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1318</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10937</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -2436,97 +2436,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2549,97 +2549,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>419791</t>
+          <t>419306</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>448523</t>
+          <t>448807</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>515980</t>
+          <t>515934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>559922</t>
+          <t>558877</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>945972</t>
+          <t>948060</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>997871</t>
+          <t>1000478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18123</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>38309</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34004</t>
+          <t>34567</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>60613</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>58003</t>
+          <t>59018</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>92077</t>
+          <t>91617</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>19444</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39347</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>45484</t>
+          <t>46902</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>77081</t>
+          <t>77364</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>71283</t>
+          <t>70831</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>107950</t>
+          <t>108646</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18651</t>
+          <t>19371</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17208</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>39391</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26404</t>
+          <t>26568</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51787</t>
+          <t>51851</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>3407</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1137</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10513</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,03%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2012</t>
+          <t>Población según el grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>305948</t>
+          <t>304491</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>342284</t>
+          <t>342551</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>398850</t>
+          <t>400480</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>448023</t>
+          <t>448136</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>63,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>717007</t>
+          <t>717304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>779932</t>
+          <t>779669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,33%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9097</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26986</t>
+          <t>27802</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>26820</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50924</t>
+          <t>50039</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>39065</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68686</t>
+          <t>67930</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37486</t>
+          <t>37285</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66971</t>
+          <t>67535</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>99543</t>
+          <t>101066</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140254</t>
+          <t>142217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>145653</t>
+          <t>145369</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>197931</t>
+          <t>196503</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,73%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9742</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29069</t>
+          <t>29351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29138</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52492</t>
+          <t>54460</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42971</t>
+          <t>45959</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74941</t>
+          <t>77126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10451</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6402</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23336</t>
+          <t>23106</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10471</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28984</t>
+          <t>28942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>96053</t>
+          <t>95909</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110795</t>
+          <t>110983</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59336</t>
+          <t>58579</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73695</t>
+          <t>73635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160359</t>
+          <t>160098</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181529</t>
+          <t>181342</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>12233</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16732</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>10648</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5126</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16800</t>
+          <t>17589</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8843</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>24556</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6918</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>5476</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8506</t>
+          <t>9022</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7838</t>
+          <t>7496</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46549</t>
+          <t>46520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6913</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -5282,97 +5282,97 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>7114</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>9,96%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>31,98%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>2215</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>6585</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>9,96%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>7716</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>4,54%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>29,6%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>2215</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>8009</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>4,54%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>15,8%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5753</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6100</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -5508,97 +5508,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2331</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>433822</t>
+          <t>432743</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>473792</t>
+          <t>473497</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>482788</t>
+          <t>481195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>533972</t>
+          <t>533219</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>65,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>930232</t>
+          <t>927555</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>993827</t>
+          <t>994746</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33088</t>
+          <t>33858</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30330</t>
+          <t>30855</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55896</t>
+          <t>55382</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50917</t>
+          <t>49658</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>81944</t>
+          <t>82446</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,34%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42597</t>
+          <t>42738</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>72331</t>
+          <t>72738</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112141</t>
+          <t>113898</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>157349</t>
+          <t>156221</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>163545</t>
+          <t>165582</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>216560</t>
+          <t>221362</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>13182</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34847</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56157</t>
+          <t>56258</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>47520</t>
+          <t>48947</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81724</t>
+          <t>83811</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12426</t>
+          <t>12546</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7661</t>
+          <t>7445</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24973</t>
+          <t>23317</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31622</t>
+          <t>31042</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2016</t>
+          <t>Población según el grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>261650</t>
+          <t>262433</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>290353</t>
+          <t>291478</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>339768</t>
+          <t>339816</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>387724</t>
+          <t>387886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>614703</t>
+          <t>612495</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>670537</t>
+          <t>668417</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,56%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28779</t>
+          <t>30281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34863</t>
+          <t>34688</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62616</t>
+          <t>62492</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53533</t>
+          <t>53337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86094</t>
+          <t>84251</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>27062</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>49326</t>
+          <t>48919</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85694</t>
+          <t>86716</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>128131</t>
+          <t>126318</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119531</t>
+          <t>119845</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>166438</t>
+          <t>165056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12334</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28198</t>
+          <t>27499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17693</t>
+          <t>18195</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39732</t>
+          <t>41509</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34795</t>
+          <t>35130</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62935</t>
+          <t>61902</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3521</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18414</t>
+          <t>18620</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>20558</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>165446</t>
+          <t>164138</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>181976</t>
+          <t>180556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>129416</t>
+          <t>128037</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155764</t>
+          <t>155681</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>300077</t>
+          <t>302126</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332375</t>
+          <t>332501</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,36%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3649</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15813</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10843</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29146</t>
+          <t>30027</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17365</t>
+          <t>17497</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>39274</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>12435</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14061</t>
+          <t>14707</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35399</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20192</t>
+          <t>19181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44320</t>
+          <t>43061</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6290</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9762</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5517</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,62 +7820,62 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2283</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6418</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1804</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>5978</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29166</t>
+          <t>29386</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39910</t>
+          <t>39624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21559</t>
+          <t>21242</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>31545</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56379</t>
+          <t>54691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69820</t>
+          <t>69630</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10055</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14677</t>
+          <t>15375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>782</t>
+          <t>780</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -8354,97 +8354,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>6650</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6964</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>6917</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -8467,97 +8467,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>470096</t>
+          <t>469961</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>503474</t>
+          <t>505227</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>507833</t>
+          <t>508205</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>564916</t>
+          <t>562627</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>989578</t>
+          <t>992012</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1057842</t>
+          <t>1056969</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,44%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>21230</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>43462</t>
+          <t>42252</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54860</t>
+          <t>54841</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>91053</t>
+          <t>91218</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>83137</t>
+          <t>85139</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>123299</t>
+          <t>124387</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,11%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35499</t>
+          <t>35016</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59879</t>
+          <t>60059</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>105574</t>
+          <t>105608</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>153896</t>
+          <t>156240</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>149292</t>
+          <t>148542</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>200583</t>
+          <t>200042</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>13710</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29922</t>
+          <t>30588</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>21612</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45675</t>
+          <t>44635</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38848</t>
+          <t>39873</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66551</t>
+          <t>69101</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6965</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>19074</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22390</t>
+          <t>21882</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2023</t>
+          <t>Población según el grado de dependencia funcional para actividades básicas de la vida diaria (Barthel) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>173704</t>
+          <t>174060</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>198204</t>
+          <t>196831</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,96%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,13%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>247302</t>
+          <t>246828</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>277877</t>
+          <t>276276</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>429493</t>
+          <t>428802</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>468260</t>
+          <t>467804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19925</t>
+          <t>20349</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35854</t>
+          <t>36220</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72125</t>
+          <t>72337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94673</t>
+          <t>95709</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>94902</t>
+          <t>95895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>124071</t>
+          <t>125583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32183</t>
+          <t>32696</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>51380</t>
+          <t>50716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85603</t>
+          <t>86715</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>110820</t>
+          <t>109107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>122754</t>
+          <t>123006</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>153803</t>
+          <t>154915</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>8221</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18057</t>
+          <t>19561</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37838</t>
+          <t>37889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57459</t>
+          <t>57922</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48208</t>
+          <t>48936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>70797</t>
+          <t>73043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>336</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2978</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9888</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11754</t>
+          <t>11082</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>216725</t>
+          <t>217585</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>236648</t>
+          <t>236164</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>345587</t>
+          <t>343018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>436708</t>
+          <t>434715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>577494</t>
+          <t>576937</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>680953</t>
+          <t>678947</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,18%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15189</t>
+          <t>15235</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28978</t>
+          <t>28655</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>8264</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52990</t>
+          <t>54412</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21449</t>
+          <t>21373</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72856</t>
+          <t>72118</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>12458</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>25178</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6768</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44452</t>
+          <t>45088</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17436</t>
+          <t>18671</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61304</t>
+          <t>61153</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10671,7 +10671,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>17079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5470</t>
+          <t>5734</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23384</t>
+          <t>23839</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -10744,97 +10744,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1229</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2479</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>442</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2422</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2492</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2844</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85985</t>
+          <t>85770</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96911</t>
+          <t>96952</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>54261</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63186</t>
+          <t>63069</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>75,5%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143752</t>
+          <t>143028</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158149</t>
+          <t>158630</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12872</t>
+          <t>12030</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3935</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11315</t>
+          <t>11102</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9555</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21141</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>2489</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11119</t>
+          <t>11118</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2709</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>9203</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>16401</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>816</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11348,62 +11348,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
     </row>
@@ -11426,97 +11426,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1192</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>488538</t>
+          <t>487939</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>521335</t>
+          <t>522431</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>632618</t>
+          <t>634057</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>853267</t>
+          <t>859508</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1154855</t>
+          <t>1150953</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1399766</t>
+          <t>1388041</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>83,24%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45623</t>
+          <t>44984</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68185</t>
+          <t>68332</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>64518</t>
+          <t>59935</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>153077</t>
+          <t>150762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>101757</t>
+          <t>109332</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>203015</t>
+          <t>205363</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>53251</t>
+          <t>52305</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>77368</t>
+          <t>76298</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>66943</t>
+          <t>62394</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>164265</t>
+          <t>163607</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114668</t>
+          <t>121635</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>224470</t>
+          <t>224305</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,45%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26838</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>27642</t>
+          <t>29212</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73165</t>
+          <t>73044</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>46990</t>
+          <t>48540</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>90891</t>
+          <t>91470</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>339</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3406</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>2816</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12163,7 +12163,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12411</t>
+          <t>11800</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/barthel_r-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/barthel_r-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>304610</t>
+          <t>302473</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>329192</t>
+          <t>329334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>439678</t>
+          <t>439977</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>481240</t>
+          <t>480258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,81%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>753379</t>
+          <t>753699</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>799743</t>
+          <t>801584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>12219</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30397</t>
+          <t>29966</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32751</t>
+          <t>32422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>59051</t>
+          <t>59162</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49040</t>
+          <t>48198</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>80669</t>
+          <t>79870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17347</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35500</t>
+          <t>35417</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40386</t>
+          <t>39878</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69180</t>
+          <t>69480</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64089</t>
+          <t>61605</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96635</t>
+          <t>96217</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17346</t>
+          <t>16985</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16505</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37999</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25629</t>
+          <t>25911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48641</t>
+          <t>49974</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>892</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9785</t>
+          <t>8294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11466</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>74774</t>
+          <t>75200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84743</t>
+          <t>84667</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47687</t>
+          <t>47322</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58777</t>
+          <t>58900</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,65%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126670</t>
+          <t>126954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141853</t>
+          <t>141698</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1720</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2926</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14446</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5868</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1071</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8959</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>10972</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,77 +1774,77 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5266</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>7187</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>4,78%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>914</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4578</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,36%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1723</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>5650</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5762</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>31073</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40229</t>
+          <t>40247</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17952</t>
+          <t>17801</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25607</t>
+          <t>25633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52519</t>
+          <t>52757</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>64667</t>
+          <t>64554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>8585</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4824</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9857</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7678</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>419306</t>
+          <t>418670</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>448807</t>
+          <t>447671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>515934</t>
+          <t>514436</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>558877</t>
+          <t>558410</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>948060</t>
+          <t>948531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1000478</t>
+          <t>1000839</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17645</t>
+          <t>19008</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38309</t>
+          <t>38177</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>34970</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>61542</t>
+          <t>61466</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>59018</t>
+          <t>56690</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91617</t>
+          <t>89687</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19444</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40544</t>
+          <t>41248</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>46902</t>
+          <t>47001</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>77364</t>
+          <t>76922</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>70831</t>
+          <t>71013</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>108646</t>
+          <t>108104</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6364</t>
+          <t>6326</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19371</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17360</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39391</t>
+          <t>39238</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>26568</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>50319</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1137</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>10309</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12129</t>
+          <t>11824</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>304491</t>
+          <t>305976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>342551</t>
+          <t>341696</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>400480</t>
+          <t>400252</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>448136</t>
+          <t>446796</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>717304</t>
+          <t>717952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>779669</t>
+          <t>778164</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,19%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>8299</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>25679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26820</t>
+          <t>27394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50039</t>
+          <t>51216</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>39676</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>67930</t>
+          <t>68074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>37285</t>
+          <t>36146</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67535</t>
+          <t>65222</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>101066</t>
+          <t>99485</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>142217</t>
+          <t>140535</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>145369</t>
+          <t>148319</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>196503</t>
+          <t>197400</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10610</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29351</t>
+          <t>29626</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54460</t>
+          <t>54371</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45959</t>
+          <t>44381</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>77126</t>
+          <t>77383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>11143</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6443</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23106</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10374</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28942</t>
+          <t>27759</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95909</t>
+          <t>97277</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110983</t>
+          <t>111589</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>58579</t>
+          <t>57672</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73635</t>
+          <t>72967</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>160098</t>
+          <t>160235</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181342</t>
+          <t>181504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,97%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>904</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10214</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>11712</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17589</t>
+          <t>17900</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>9554</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>24556</t>
+          <t>24567</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>6648</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5476</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>6044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46520</t>
+          <t>45929</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,25%</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>432743</t>
+          <t>433418</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>473497</t>
+          <t>473366</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>481195</t>
+          <t>481981</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>533219</t>
+          <t>533517</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>927555</t>
+          <t>929736</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>994746</t>
+          <t>997033</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,72%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13814</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33858</t>
+          <t>34370</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30855</t>
+          <t>30775</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>55382</t>
+          <t>55090</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49658</t>
+          <t>50277</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82446</t>
+          <t>80600</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42738</t>
+          <t>41795</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>72738</t>
+          <t>73249</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>113898</t>
+          <t>113462</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156221</t>
+          <t>153419</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>165582</t>
+          <t>161693</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>221362</t>
+          <t>213575</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13182</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>33963</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>31183</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>56258</t>
+          <t>57250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48947</t>
+          <t>48264</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83811</t>
+          <t>82654</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>12546</t>
+          <t>12259</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7445</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23317</t>
+          <t>24172</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12016</t>
+          <t>12650</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>31042</t>
+          <t>31070</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,7 +6275,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>262433</t>
+          <t>262991</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>291478</t>
+          <t>291458</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>339816</t>
+          <t>337840</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>387886</t>
+          <t>387892</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>612495</t>
+          <t>612666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>668417</t>
+          <t>669729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13729</t>
+          <t>13523</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30281</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34688</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62492</t>
+          <t>64501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53337</t>
+          <t>54623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>84251</t>
+          <t>86396</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27062</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48919</t>
+          <t>47680</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>86716</t>
+          <t>85597</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>126318</t>
+          <t>126755</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>119845</t>
+          <t>119313</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>165056</t>
+          <t>165300</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27499</t>
+          <t>28039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18195</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41509</t>
+          <t>42005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35130</t>
+          <t>33918</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61902</t>
+          <t>63034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3671</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18620</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20558</t>
+          <t>19845</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>164138</t>
+          <t>164599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>180556</t>
+          <t>180759</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>128037</t>
+          <t>128217</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>155681</t>
+          <t>155695</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>302126</t>
+          <t>300542</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>332501</t>
+          <t>332188</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,38%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,28%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14775</t>
+          <t>15203</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11685</t>
+          <t>11183</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30027</t>
+          <t>31854</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17497</t>
+          <t>17166</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>39274</t>
+          <t>40383</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12435</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14707</t>
+          <t>14405</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>35604</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19462</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43061</t>
+          <t>43837</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -7677,7 +7677,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29386</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>39624</t>
+          <t>39687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>20459</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31545</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54691</t>
+          <t>55750</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69630</t>
+          <t>69573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,9%</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>15024</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>775</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>728</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -8394,7 +8394,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8409,7 +8409,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>469961</t>
+          <t>468638</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>505227</t>
+          <t>505049</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>508205</t>
+          <t>506032</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>562627</t>
+          <t>565026</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>992012</t>
+          <t>991572</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1056969</t>
+          <t>1059085</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,59%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21230</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42252</t>
+          <t>41797</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>54841</t>
+          <t>55575</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>91218</t>
+          <t>92099</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>85139</t>
+          <t>83818</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>124387</t>
+          <t>124154</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35016</t>
+          <t>35310</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>60059</t>
+          <t>59580</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>105608</t>
+          <t>106399</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>156240</t>
+          <t>151840</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>148542</t>
+          <t>150495</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>200042</t>
+          <t>202765</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13710</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30588</t>
+          <t>29550</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21612</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44635</t>
+          <t>44887</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39873</t>
+          <t>39045</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>69101</t>
+          <t>67897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>823</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>6203</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>21882</t>
+          <t>22639</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>185841</t>
+          <t>201442</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>174060</t>
+          <t>189297</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>196831</t>
+          <t>213930</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>262293</t>
+          <t>281352</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>246828</t>
+          <t>264538</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>276276</t>
+          <t>298534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>56,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,22 +9675,22 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>448133</t>
+          <t>482795</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>428802</t>
+          <t>461663</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>467804</t>
+          <t>506807</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>58,77%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -9718,22 +9718,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27069</t>
+          <t>29243</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20349</t>
+          <t>21923</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36220</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>83120</t>
+          <t>89268</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72337</t>
+          <t>77509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95709</t>
+          <t>103545</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>110189</t>
+          <t>118512</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>95895</t>
+          <t>103880</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>125583</t>
+          <t>134091</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40889</t>
+          <t>42766</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32696</t>
+          <t>34267</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50716</t>
+          <t>53684</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>97257</t>
+          <t>105616</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>86715</t>
+          <t>93224</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>109107</t>
+          <t>119940</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>138147</t>
+          <t>148382</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>123006</t>
+          <t>132864</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>154915</t>
+          <t>166734</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,31%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19561</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46617</t>
+          <t>50389</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37889</t>
+          <t>40623</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>57922</t>
+          <t>61184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>59049</t>
+          <t>63712</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>52257</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73043</t>
+          <t>76407</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>338</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3461</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5814</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9957</t>
+          <t>10681</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,17 +10127,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>7453</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4195</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11082</t>
+          <t>12570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>267386</t>
+          <t>287936</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>267386</t>
+          <t>287936</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>267386</t>
+          <t>287936</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>495101</t>
+          <t>532918</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>495101</t>
+          <t>532918</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>495101</t>
+          <t>532918</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>762486</t>
+          <t>820854</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>762486</t>
+          <t>820854</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>762486</t>
+          <t>820854</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,69 +10287,69 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>227597</t>
+          <t>254942</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>217585</t>
+          <t>243577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>236164</t>
+          <t>264376</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>80,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87,02%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>210871</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>199795</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>220827</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>76,04%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>72,05%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
           <t>79,63%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>396854</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>343018</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>434715</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>87,15%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>75,32%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>95,46%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>757</t>
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>624450</t>
+          <t>465812</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>576937</t>
+          <t>448444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>678947</t>
+          <t>478798</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21263</t>
+          <t>22957</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15235</t>
+          <t>16674</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28655</t>
+          <t>31526</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27353</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>22274</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54412</t>
+          <t>37736</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>48616</t>
+          <t>52819</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>43348</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72118</t>
+          <t>64852</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>13464</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25178</t>
+          <t>27320</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>22707</t>
+          <t>27514</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>21367</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45088</t>
+          <t>36098</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40741</t>
+          <t>46841</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18671</t>
+          <t>38384</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61153</t>
+          <t>59137</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>12534</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8037</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17079</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23839</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -10774,7 +10774,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>457</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>457</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -10819,12 +10819,12 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>273257</t>
+          <t>303825</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>455392</t>
+          <t>277301</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>455392</t>
+          <t>277301</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>455392</t>
+          <t>277301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>728649</t>
+          <t>581126</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>728649</t>
+          <t>581126</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>728649</t>
+          <t>581126</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>92142</t>
+          <t>103583</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>85770</t>
+          <t>95934</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96952</t>
+          <t>109141</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>59272</t>
+          <t>68409</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54261</t>
+          <t>62394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>63069</t>
+          <t>72773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>151414</t>
+          <t>171992</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>143028</t>
+          <t>163566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158630</t>
+          <t>179991</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,22%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7183</t>
+          <t>8698</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3974</t>
+          <t>5055</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11102</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13988</t>
+          <t>17457</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>11677</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20142</t>
+          <t>24444</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5503</t>
+          <t>5942</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2489</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>11865</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5247</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9203</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>11629</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16401</t>
+          <t>18958</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -11318,12 +11318,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>659</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -11388,12 +11388,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>104986</t>
+          <t>118881</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>176311</t>
+          <t>201736</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>505579</t>
+          <t>559967</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>487939</t>
+          <t>540989</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>522431</t>
+          <t>578507</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>76,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>718418</t>
+          <t>560632</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>634057</t>
+          <t>539896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>859508</t>
+          <t>583310</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>60,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1223997</t>
+          <t>1120599</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1150953</t>
+          <t>1090447</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1388041</t>
+          <t>1145780</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>71,45%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>55515</t>
+          <t>60899</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44984</t>
+          <t>49464</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68332</t>
+          <t>74491</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>117278</t>
+          <t>127889</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>59935</t>
+          <t>115025</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>150762</t>
+          <t>143324</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>172793</t>
+          <t>188788</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>109332</t>
+          <t>169252</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>205363</t>
+          <t>210099</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>64426</t>
+          <t>68034</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>52305</t>
+          <t>54968</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76298</t>
+          <t>81467</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>125211</t>
+          <t>138818</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62394</t>
+          <t>122779</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>163607</t>
+          <t>154933</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>189638</t>
+          <t>206852</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>121635</t>
+          <t>186727</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>224305</t>
+          <t>230888</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -11990,22 +11990,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>20581</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12726</t>
+          <t>13994</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27232</t>
+          <t>28879</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>54654</t>
+          <t>58986</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29212</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73044</t>
+          <t>71205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>73607</t>
+          <t>79567</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48540</t>
+          <t>67008</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91470</t>
+          <t>94036</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -12103,22 +12103,22 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1154</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>339</t>
+          <t>341</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>3774</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2816</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>11139</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11800</t>
+          <t>12819</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>645628</t>
+          <t>710643</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>645628</t>
+          <t>710643</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>645628</t>
+          <t>710643</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1021817</t>
+          <t>893074</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1021817</t>
+          <t>893074</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1021817</t>
+          <t>893074</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1667445</t>
+          <t>1603716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1667445</t>
+          <t>1603716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1667445</t>
+          <t>1603716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
